--- a/AWS  LAB Credentials.xlsx
+++ b/AWS  LAB Credentials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Ahmad\Desktop\AWS SA Professional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7548A50-A8B4-4DB9-ADC3-D017DBD81A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF9B121-1043-4139-BB71-AF7B42559D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9BC01C13-7A80-4246-B594-354B9BD9D5F3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>Participant Name</t>
   </si>
@@ -300,6 +300,18 @@
   </si>
   <si>
     <t>Satyanarayana jamjam</t>
+  </si>
+  <si>
+    <t>Swarup Fule</t>
+  </si>
+  <si>
+    <t>user21</t>
+  </si>
+  <si>
+    <t>Europe (Zurich)</t>
+  </si>
+  <si>
+    <t>eu-central-2</t>
   </si>
 </sst>
 </file>
@@ -764,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C107E21C-3C0C-4C1B-B9B1-06BE273296C4}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1218,6 +1230,26 @@
         <v>59</v>
       </c>
     </row>
+    <row r="22" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -1232,8 +1264,10 @@
     <hyperlink ref="B18:B20" r:id="rId9" display="https://ahmadzahoory.signin.aws.amazon.com/console" xr:uid="{7461786A-98EE-44E3-94F1-0396FBE46B2C}"/>
     <hyperlink ref="D21" r:id="rId10" xr:uid="{FB3A0D97-CC5D-4676-AD12-0B6A567605FE}"/>
     <hyperlink ref="B21" r:id="rId11" xr:uid="{ED9FAFE6-9554-4CD7-BD39-6ADF166E7729}"/>
+    <hyperlink ref="D22" r:id="rId12" xr:uid="{F30CA247-B545-4029-96F7-C159C2236C74}"/>
+    <hyperlink ref="B22" r:id="rId13" xr:uid="{3911B83B-5423-47F4-B153-FB106CFB6135}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId12"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>